--- a/results/anova_results.xlsx
+++ b/results/anova_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/judyabuel/Desktop/GitHub/cloud_amp_correlation/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36E5251-7F20-3641-9E02-2F5BDAAE0C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64452A32-FE37-524A-A3AA-2BA5E0CA50AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="17460" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="600" windowWidth="17460" windowHeight="14620" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ANOVA_2way" sheetId="1" r:id="rId1"/>
@@ -117,12 +117,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -137,11 +143,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1068,6 +1079,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2319,13 +2331,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="3.5" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="3"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -2343,7 +2363,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -2369,7 +2389,7 @@
       <c r="E2">
         <v>4.476693295634969</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>4.3067112849766137E-2</v>
       </c>
       <c r="G2" t="s">
@@ -2395,7 +2415,7 @@
       <c r="E3">
         <v>1.554010887210409</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>0.22251986081667119</v>
       </c>
       <c r="G3" t="s">
@@ -2421,7 +2441,7 @@
       <c r="E4">
         <v>6.7566526810305394</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <v>1.453645319613643E-2</v>
       </c>
       <c r="G4" t="s">
@@ -2451,50 +2471,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1.407449454638638</v>
-      </c>
-      <c r="D6">
-        <v>1.407449454638638</v>
-      </c>
-      <c r="E6">
-        <v>2.1178140445797569</v>
-      </c>
-      <c r="F6">
-        <v>0.15633459726773441</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>0.19021206136218169</v>
+        <v>1.407449454638638</v>
       </c>
       <c r="D7">
-        <v>0.19021206136218169</v>
+        <v>1.407449454638638</v>
       </c>
       <c r="E7">
-        <v>0.28621544715062069</v>
-      </c>
-      <c r="F7">
-        <v>0.59673479257414619</v>
+        <v>2.1178140445797569</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.15633459726773441</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
@@ -2505,22 +2499,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>3.1479116067777908</v>
+        <v>0.19021206136218169</v>
       </c>
       <c r="D8">
-        <v>3.1479116067777908</v>
+        <v>0.19021206136218169</v>
       </c>
       <c r="E8">
-        <v>4.7367181748216352</v>
-      </c>
-      <c r="F8">
-        <v>3.7813123930219593E-2</v>
+        <v>0.28621544715062069</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.59673479257414619</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
@@ -2531,16 +2525,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>19.272718626540101</v>
+        <v>3.1479116067777908</v>
       </c>
       <c r="D9">
-        <v>0.66457650436345161</v>
+        <v>3.1479116067777908</v>
+      </c>
+      <c r="E9">
+        <v>4.7367181748216352</v>
+      </c>
+      <c r="F9" s="4">
+        <v>3.7813123930219593E-2</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
@@ -2551,74 +2551,42 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C10">
-        <v>415.98437814726708</v>
+        <v>19.272718626540101</v>
       </c>
       <c r="D10">
-        <v>415.98437814726708</v>
-      </c>
-      <c r="E10">
-        <v>76.242497144463329</v>
-      </c>
-      <c r="F10">
-        <v>1.30259569409316E-9</v>
+        <v>0.66457650436345161</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>0.61210835895789462</v>
-      </c>
-      <c r="D11">
-        <v>0.61210835895789462</v>
-      </c>
-      <c r="E11">
-        <v>0.1121885153904211</v>
-      </c>
-      <c r="F11">
-        <v>0.74007690708883778</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.67773232711467513</v>
+        <v>415.98437814726708</v>
       </c>
       <c r="D12">
-        <v>0.67773232711467513</v>
+        <v>415.98437814726708</v>
       </c>
       <c r="E12">
-        <v>0.12421621514945</v>
-      </c>
-      <c r="F12">
-        <v>0.72705451493312001</v>
+        <v>76.242497144463329</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1.30259569409316E-9</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -2629,16 +2597,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>158.2260211573722</v>
+        <v>0.61210835895789462</v>
       </c>
       <c r="D13">
-        <v>5.4560696950818004</v>
+        <v>0.61210835895789462</v>
+      </c>
+      <c r="E13">
+        <v>0.1121885153904211</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.74007690708883778</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -2649,25 +2623,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14">
-        <v>1.2409362295069311</v>
+        <v>0.67773232711467513</v>
       </c>
       <c r="D14">
-        <v>1.2409362295069311</v>
+        <v>0.67773232711467513</v>
       </c>
       <c r="E14">
-        <v>2.1075788948969341</v>
-      </c>
-      <c r="F14">
-        <v>0.15730454636223251</v>
+        <v>0.12421621514945</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.72705451493312001</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
         <v>10</v>
@@ -2675,68 +2649,42 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C15">
-        <v>0.1526867290526735</v>
+        <v>158.2260211573722</v>
       </c>
       <c r="D15">
-        <v>0.1526867290526735</v>
-      </c>
-      <c r="E15">
-        <v>0.25931979422514212</v>
-      </c>
-      <c r="F15">
-        <v>0.61444102283583013</v>
+        <v>5.4560696950818004</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>2.6355333646897421</v>
-      </c>
-      <c r="D16">
-        <v>2.6355333646897421</v>
-      </c>
-      <c r="E16">
-        <v>4.4761321042450692</v>
-      </c>
-      <c r="F16">
-        <v>4.3079294302946637E-2</v>
-      </c>
-      <c r="G16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B17">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>17.075114361240029</v>
+        <v>1.2409362295069311</v>
       </c>
       <c r="D17">
-        <v>0.58879704693931123</v>
+        <v>1.2409362295069311</v>
+      </c>
+      <c r="E17">
+        <v>2.1075788948969341</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.15730454636223251</v>
       </c>
       <c r="G17" t="s">
         <v>16</v>
@@ -2747,25 +2695,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18">
-        <v>56.399980760402791</v>
+        <v>0.1526867290526735</v>
       </c>
       <c r="D18">
-        <v>56.399980760402791</v>
+        <v>0.1526867290526735</v>
       </c>
       <c r="E18">
-        <v>55.824197477451932</v>
-      </c>
-      <c r="F18">
-        <v>3.1050408507788358E-8</v>
+        <v>0.25931979422514212</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.61444102283583013</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
         <v>10</v>
@@ -2773,25 +2721,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>0.29625220225622462</v>
+        <v>2.6355333646897421</v>
       </c>
       <c r="D19">
-        <v>0.29625220225622462</v>
+        <v>2.6355333646897421</v>
       </c>
       <c r="E19">
-        <v>0.29322778516783671</v>
-      </c>
-      <c r="F19">
-        <v>0.59229573923436762</v>
+        <v>4.4761321042450692</v>
+      </c>
+      <c r="F19" s="4">
+        <v>4.3079294302946637E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
         <v>10</v>
@@ -2799,47 +2747,21 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C20">
-        <v>0.19814592551116589</v>
+        <v>17.075114361240029</v>
       </c>
       <c r="D20">
-        <v>0.19814592551116589</v>
-      </c>
-      <c r="E20">
-        <v>0.19612306823433759</v>
-      </c>
-      <c r="F20">
-        <v>0.661154472239319</v>
+        <v>0.58879704693931123</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21">
-        <v>29</v>
-      </c>
-      <c r="C21">
-        <v>29.29911249888222</v>
-      </c>
-      <c r="D21">
-        <v>1.010314224099387</v>
-      </c>
-      <c r="G21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2851,19 +2773,19 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>1.407449454645449</v>
+        <v>56.399980760402791</v>
       </c>
       <c r="D22">
-        <v>1.407449454645449</v>
+        <v>56.399980760402791</v>
       </c>
       <c r="E22">
-        <v>2.117814044611519</v>
-      </c>
-      <c r="F22">
-        <v>0.15633459726473531</v>
+        <v>55.824197477451932</v>
+      </c>
+      <c r="F22" s="4">
+        <v>3.1050408507788358E-8</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
         <v>10</v>
@@ -2877,19 +2799,19 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>0.1902120613648251</v>
+        <v>0.29625220225622462</v>
       </c>
       <c r="D23">
-        <v>0.1902120613648251</v>
+        <v>0.29625220225622462</v>
       </c>
       <c r="E23">
-        <v>0.2862154471575058</v>
-      </c>
-      <c r="F23">
-        <v>0.59673479256975326</v>
+        <v>0.29322778516783671</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.59229573923436762</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
         <v>10</v>
@@ -2903,19 +2825,19 @@
         <v>1</v>
       </c>
       <c r="C24">
-        <v>3.1479116067343811</v>
+        <v>0.19814592551116589</v>
       </c>
       <c r="D24">
-        <v>3.1479116067343811</v>
+        <v>0.19814592551116589</v>
       </c>
       <c r="E24">
-        <v>4.7367181748044329</v>
-      </c>
-      <c r="F24">
-        <v>3.7813123930542779E-2</v>
+        <v>0.19612306823433759</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.661154472239319</v>
       </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
         <v>10</v>
@@ -2929,94 +2851,68 @@
         <v>29</v>
       </c>
       <c r="C25">
-        <v>19.272718626344311</v>
+        <v>29.29911249888222</v>
       </c>
       <c r="D25">
-        <v>0.66457650435670046</v>
+        <v>1.010314224099387</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>178.32945432164311</v>
-      </c>
-      <c r="D26">
-        <v>178.32945432164311</v>
-      </c>
-      <c r="E26">
-        <v>4.3665536923605606</v>
-      </c>
-      <c r="F26">
-        <v>4.9002405285512592E-2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>61.904154523236627</v>
+        <v>1.407449454645449</v>
       </c>
       <c r="D27">
-        <v>61.904154523236627</v>
+        <v>1.407449454645449</v>
       </c>
       <c r="E27">
-        <v>1.515777724628474</v>
-      </c>
-      <c r="F27">
-        <v>0.23187044822730271</v>
+        <v>2.117814044611519</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0.15633459726473531</v>
       </c>
       <c r="G27" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>53.06526661407559</v>
+        <v>0.1902120613648251</v>
       </c>
       <c r="D28">
-        <v>26.532633307037791</v>
+        <v>0.1902120613648251</v>
       </c>
       <c r="E28">
-        <v>0.64967488615723146</v>
-      </c>
-      <c r="F28">
-        <v>0.53239565038688397</v>
+        <v>0.2862154471575058</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0.59673479256975326</v>
       </c>
       <c r="G28" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -3027,94 +2923,62 @@
         <v>1</v>
       </c>
       <c r="C29">
-        <v>247.87904570234639</v>
+        <v>3.1479116067343811</v>
       </c>
       <c r="D29">
-        <v>247.87904570234639</v>
+        <v>3.1479116067343811</v>
       </c>
       <c r="E29">
-        <v>6.0695366695743278</v>
-      </c>
-      <c r="F29">
-        <v>2.2471548795451709E-2</v>
+        <v>4.7367181748044329</v>
+      </c>
+      <c r="F29" s="4">
+        <v>3.7813123930542779E-2</v>
       </c>
       <c r="G29" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C30">
-        <v>173.9124184371635</v>
+        <v>19.272718626344311</v>
       </c>
       <c r="D30">
-        <v>86.956209218581733</v>
-      </c>
-      <c r="E30">
-        <v>2.1291993399600342</v>
-      </c>
-      <c r="F30">
-        <v>0.1438936234231096</v>
+        <v>0.66457650435670046</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31">
-        <v>60.954177859431631</v>
-      </c>
-      <c r="D31">
-        <v>30.477088929715819</v>
-      </c>
-      <c r="E31">
-        <v>0.74625835482243408</v>
-      </c>
-      <c r="F31">
-        <v>0.48629863543968088</v>
-      </c>
-      <c r="G31" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>30.921239499795089</v>
+        <v>178.32945432164311</v>
       </c>
       <c r="D32">
-        <v>15.460619749897541</v>
+        <v>178.32945432164311</v>
       </c>
       <c r="E32">
-        <v>0.37856688628303831</v>
-      </c>
-      <c r="F32">
-        <v>0.68942167599589943</v>
+        <v>4.3665536923605606</v>
+      </c>
+      <c r="F32" s="4">
+        <v>4.9002405285512592E-2</v>
       </c>
       <c r="G32" t="s">
         <v>9</v>
@@ -3125,16 +2989,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B33">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>857.63712176638785</v>
+        <v>61.904154523236627</v>
       </c>
       <c r="D33">
-        <v>40.839862941256563</v>
+        <v>61.904154523236627</v>
+      </c>
+      <c r="E33">
+        <v>1.515777724628474</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.23187044822730271</v>
       </c>
       <c r="G33" t="s">
         <v>9</v>
@@ -3145,25 +3015,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>1.407449454638638</v>
+        <v>53.06526661407559</v>
       </c>
       <c r="D34">
-        <v>1.407449454638638</v>
+        <v>26.532633307037791</v>
       </c>
       <c r="E34">
-        <v>2.152360422890629</v>
-      </c>
-      <c r="F34">
-        <v>0.1571681508513679</v>
+        <v>0.64967488615723146</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.53239565038688397</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
         <v>19</v>
@@ -3171,25 +3041,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>0.19021206136218169</v>
+        <v>247.87904570234639</v>
       </c>
       <c r="D35">
-        <v>0.19021206136218169</v>
+        <v>247.87904570234639</v>
       </c>
       <c r="E35">
-        <v>0.290884274019999</v>
-      </c>
-      <c r="F35">
-        <v>0.595327158497992</v>
+        <v>6.0695366695743278</v>
+      </c>
+      <c r="F35" s="4">
+        <v>2.2471548795451709E-2</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H35" t="s">
         <v>19</v>
@@ -3197,25 +3067,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>2.803261262921664</v>
+        <v>173.9124184371635</v>
       </c>
       <c r="D36">
-        <v>1.401630631460832</v>
+        <v>86.956209218581733</v>
       </c>
       <c r="E36">
-        <v>2.143461911704716</v>
-      </c>
-      <c r="F36">
-        <v>0.142198361456468</v>
+        <v>2.1291993399600342</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0.1438936234231096</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
@@ -3223,25 +3093,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>2.8415365931513401</v>
+        <v>60.954177859431631</v>
       </c>
       <c r="D37">
-        <v>2.8415365931513401</v>
+        <v>30.477088929715819</v>
       </c>
       <c r="E37">
-        <v>4.3454568710353429</v>
-      </c>
-      <c r="F37">
-        <v>4.9503523876429853E-2</v>
+        <v>0.74625835482243408</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0.48629863543968088</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H37" t="s">
         <v>19</v>
@@ -3249,25 +3119,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>0.45756801409861181</v>
+        <v>30.921239499795089</v>
       </c>
       <c r="D38">
-        <v>0.2287840070493059</v>
+        <v>15.460619749897541</v>
       </c>
       <c r="E38">
-        <v>0.34987092470023151</v>
-      </c>
-      <c r="F38">
-        <v>0.70880967686823981</v>
+        <v>0.37856688628303831</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.68942167599589943</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H38" t="s">
         <v>19</v>
@@ -3275,68 +3145,42 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C39">
-        <v>1.8893688926700321</v>
+        <v>857.63712176638785</v>
       </c>
       <c r="D39">
-        <v>0.94468444633501625</v>
-      </c>
-      <c r="E39">
-        <v>1.444671002365683</v>
-      </c>
-      <c r="F39">
-        <v>0.25832035053725999</v>
+        <v>40.839862941256563</v>
       </c>
       <c r="G39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H39" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40">
-        <v>2</v>
-      </c>
-      <c r="C40">
-        <v>0.69679083173874978</v>
-      </c>
-      <c r="D40">
-        <v>0.34839541586937489</v>
-      </c>
-      <c r="E40">
-        <v>0.53278823062693481</v>
-      </c>
-      <c r="F40">
-        <v>0.59469211113404108</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B41">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>13.732104638737489</v>
+        <v>1.407449454638638</v>
       </c>
       <c r="D41">
-        <v>0.65390974470178531</v>
+        <v>1.407449454638638</v>
+      </c>
+      <c r="E41">
+        <v>2.152360422890629</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.1571681508513679</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
@@ -3347,25 +3191,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>415.98437814726708</v>
+        <v>0.19021206136218169</v>
       </c>
       <c r="D42">
-        <v>415.98437814726708</v>
+        <v>0.19021206136218169</v>
       </c>
       <c r="E42">
-        <v>99.873812513161184</v>
-      </c>
-      <c r="F42">
-        <v>1.958959880282291E-9</v>
+        <v>0.290884274019999</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0.595327158497992</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
         <v>19</v>
@@ -3373,25 +3217,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>0.61210835895789462</v>
+        <v>2.803261262921664</v>
       </c>
       <c r="D43">
-        <v>0.61210835895789462</v>
+        <v>1.401630631460832</v>
       </c>
       <c r="E43">
-        <v>0.1469612771339624</v>
-      </c>
-      <c r="F43">
-        <v>0.70530972629348976</v>
+        <v>2.143461911704716</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.142198361456468</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
         <v>19</v>
@@ -3399,25 +3243,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>32.619318052469943</v>
+        <v>2.8415365931513401</v>
       </c>
       <c r="D44">
-        <v>16.309659026234971</v>
+        <v>2.8415365931513401</v>
       </c>
       <c r="E44">
-        <v>3.915790864538454</v>
-      </c>
-      <c r="F44">
-        <v>3.5866060077088903E-2</v>
+        <v>4.3454568710353429</v>
+      </c>
+      <c r="F44" s="4">
+        <v>4.9503523876429853E-2</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
         <v>19</v>
@@ -3425,25 +3269,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>5.4854703795396672E-3</v>
+        <v>0.45756801409861181</v>
       </c>
       <c r="D45">
-        <v>5.4854703795396672E-3</v>
+        <v>0.2287840070493059</v>
       </c>
       <c r="E45">
-        <v>1.3170082075502651E-3</v>
-      </c>
-      <c r="F45">
-        <v>0.97139340141494301</v>
+        <v>0.34987092470023151</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.70880967686823981</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
         <v>19</v>
@@ -3451,25 +3295,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
       <c r="C46">
-        <v>21.541640833993839</v>
+        <v>1.8893688926700321</v>
       </c>
       <c r="D46">
-        <v>10.770820416996919</v>
+        <v>0.94468444633501625</v>
       </c>
       <c r="E46">
-        <v>2.5859694629187508</v>
-      </c>
-      <c r="F46">
-        <v>9.9089049823563383E-2</v>
+        <v>1.444671002365683</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.25832035053725999</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
         <v>19</v>
@@ -3477,25 +3321,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47">
-        <v>10.344773281450291</v>
+        <v>0.69679083173874978</v>
       </c>
       <c r="D47">
-        <v>5.1723866407251444</v>
+        <v>0.34839541586937489</v>
       </c>
       <c r="E47">
-        <v>1.2418398400011079</v>
-      </c>
-      <c r="F47">
-        <v>0.30921321160462212</v>
+        <v>0.53278823062693481</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.59469211113404108</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
@@ -3503,47 +3347,21 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C48">
-        <v>6.9254439101421186</v>
+        <v>13.732104638737489</v>
       </c>
       <c r="D48">
-        <v>3.4627219550710602</v>
-      </c>
-      <c r="E48">
-        <v>0.83136593942847814</v>
-      </c>
-      <c r="F48">
-        <v>0.44928700485128098</v>
+        <v>0.65390974470178531</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49">
-        <v>21</v>
-      </c>
-      <c r="C49">
-        <v>87.467091936051176</v>
-      </c>
-      <c r="D49">
-        <v>4.1650996160024372</v>
-      </c>
-      <c r="G49" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3555,19 +3373,19 @@
         <v>1</v>
       </c>
       <c r="C50">
-        <v>1.2409362295069311</v>
+        <v>415.98437814726708</v>
       </c>
       <c r="D50">
-        <v>1.2409362295069311</v>
+        <v>415.98437814726708</v>
       </c>
       <c r="E50">
-        <v>2.116972058055786</v>
-      </c>
-      <c r="F50">
-        <v>0.1604602153373422</v>
+        <v>99.873812513161184</v>
+      </c>
+      <c r="F50" s="4">
+        <v>1.958959880282291E-9</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
         <v>19</v>
@@ -3581,19 +3399,19 @@
         <v>1</v>
       </c>
       <c r="C51">
-        <v>0.1526867290526735</v>
+        <v>0.61210835895789462</v>
       </c>
       <c r="D51">
-        <v>0.1526867290526735</v>
+        <v>0.61210835895789462</v>
       </c>
       <c r="E51">
-        <v>0.2604755436698602</v>
-      </c>
-      <c r="F51">
-        <v>0.61511659781730799</v>
+        <v>0.1469612771339624</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.70530972629348976</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H51" t="s">
         <v>19</v>
@@ -3607,19 +3425,19 @@
         <v>2</v>
       </c>
       <c r="C52">
-        <v>2.569762594401761</v>
+        <v>32.619318052469943</v>
       </c>
       <c r="D52">
-        <v>1.284881297200881</v>
+        <v>16.309659026234971</v>
       </c>
       <c r="E52">
-        <v>2.1919400364138881</v>
-      </c>
-      <c r="F52">
-        <v>0.13659774141296729</v>
+        <v>3.915790864538454</v>
+      </c>
+      <c r="F52" s="4">
+        <v>3.5866060077088903E-2</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
         <v>19</v>
@@ -3633,19 +3451,19 @@
         <v>1</v>
       </c>
       <c r="C53">
-        <v>2.324215489150065</v>
+        <v>5.4854703795396672E-3</v>
       </c>
       <c r="D53">
-        <v>2.324215489150065</v>
+        <v>5.4854703795396672E-3</v>
       </c>
       <c r="E53">
-        <v>3.9649896025569018</v>
-      </c>
-      <c r="F53">
-        <v>5.9623983493489061E-2</v>
+        <v>1.3170082075502651E-3</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.97139340141494301</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
         <v>19</v>
@@ -3659,19 +3477,19 @@
         <v>2</v>
       </c>
       <c r="C54">
-        <v>0.3632167849493137</v>
+        <v>21.541640833993839</v>
       </c>
       <c r="D54">
-        <v>0.18160839247465679</v>
+        <v>10.770820416996919</v>
       </c>
       <c r="E54">
-        <v>0.30981438307272002</v>
-      </c>
-      <c r="F54">
-        <v>0.73687895782584945</v>
+        <v>2.5859694629187508</v>
+      </c>
+      <c r="F54" s="3">
+        <v>9.9089049823563383E-2</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
         <v>19</v>
@@ -3685,19 +3503,19 @@
         <v>2</v>
       </c>
       <c r="C55">
-        <v>1.515729642129845</v>
+        <v>10.344773281450291</v>
       </c>
       <c r="D55">
-        <v>0.75786482106492248</v>
+        <v>5.1723866407251444</v>
       </c>
       <c r="E55">
-        <v>1.29287759663151</v>
-      </c>
-      <c r="F55">
-        <v>0.29544717144697769</v>
+        <v>1.2418398400011079</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.30921321160462212</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
         <v>19</v>
@@ -3711,19 +3529,19 @@
         <v>2</v>
       </c>
       <c r="C56">
-        <v>0.62784849565859768</v>
+        <v>6.9254439101421186</v>
       </c>
       <c r="D56">
-        <v>0.31392424782929879</v>
+        <v>3.4627219550710602</v>
       </c>
       <c r="E56">
-        <v>0.53553828569004103</v>
-      </c>
-      <c r="F56">
-        <v>0.59313788098617448</v>
+        <v>0.83136593942847814</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0.44928700485128098</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H56" t="s">
         <v>19</v>
@@ -3737,65 +3555,39 @@
         <v>21</v>
       </c>
       <c r="C57">
-        <v>12.309874719640179</v>
+        <v>87.467091936051176</v>
       </c>
       <c r="D57">
-        <v>0.58618451045905617</v>
+        <v>4.1650996160024372</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>8</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58">
-        <v>56.399980760402791</v>
-      </c>
-      <c r="D58">
-        <v>56.399980760402791</v>
-      </c>
-      <c r="E58">
-        <v>63.240723473547092</v>
-      </c>
-      <c r="F58">
-        <v>9.0608433113040592E-8</v>
-      </c>
-      <c r="G58" t="s">
-        <v>17</v>
-      </c>
-      <c r="H58" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>0.29625220225622462</v>
+        <v>1.2409362295069311</v>
       </c>
       <c r="D59">
-        <v>0.29625220225622462</v>
+        <v>1.2409362295069311</v>
       </c>
       <c r="E59">
-        <v>0.33218457433355769</v>
-      </c>
-      <c r="F59">
-        <v>0.57050203395472754</v>
+        <v>2.116972058055786</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.1604602153373422</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H59" t="s">
         <v>19</v>
@@ -3803,25 +3595,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>3.8403487137522112</v>
+        <v>0.1526867290526735</v>
       </c>
       <c r="D60">
-        <v>1.9201743568761049</v>
+        <v>0.1526867290526735</v>
       </c>
       <c r="E60">
-        <v>2.1530719317098339</v>
-      </c>
-      <c r="F60">
-        <v>0.14106844592515019</v>
+        <v>0.2604755436698602</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0.61511659781730799</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H60" t="s">
         <v>19</v>
@@ -3829,25 +3621,25 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>0.44549894357860231</v>
+        <v>2.569762594401761</v>
       </c>
       <c r="D61">
-        <v>0.44549894357860231</v>
+        <v>1.284881297200881</v>
       </c>
       <c r="E61">
-        <v>0.49953342392612787</v>
-      </c>
-      <c r="F61">
-        <v>0.48747423121554229</v>
+        <v>2.1919400364138881</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.13659774141296729</v>
       </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
         <v>19</v>
@@ -3855,25 +3647,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>3.0019840314486288</v>
+        <v>2.324215489150065</v>
       </c>
       <c r="D62">
-        <v>1.5009920157243151</v>
+        <v>2.324215489150065</v>
       </c>
       <c r="E62">
-        <v>1.6830470458079909</v>
-      </c>
-      <c r="F62">
-        <v>0.2099183803408276</v>
+        <v>3.9649896025569018</v>
+      </c>
+      <c r="F62" s="4">
+        <v>5.9623983493489061E-2</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H62" t="s">
         <v>19</v>
@@ -3881,25 +3673,25 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>2.107882035430896</v>
+        <v>0.3632167849493137</v>
       </c>
       <c r="D63">
-        <v>1.053941017715448</v>
+        <v>0.18160839247465679</v>
       </c>
       <c r="E63">
-        <v>1.1817733190711719</v>
-      </c>
-      <c r="F63">
-        <v>0.32632136311739951</v>
+        <v>0.30981438307272002</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.73687895782584945</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H63" t="s">
         <v>19</v>
@@ -3907,25 +3699,25 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>1.373112593237271</v>
+        <v>1.515729642129845</v>
       </c>
       <c r="D64">
-        <v>0.68655629661863538</v>
+        <v>0.75786482106492248</v>
       </c>
       <c r="E64">
-        <v>0.76982857650130188</v>
-      </c>
-      <c r="F64">
-        <v>0.47572490058145211</v>
+        <v>1.29287759663151</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0.29544717144697769</v>
       </c>
       <c r="G64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H64" t="s">
         <v>19</v>
@@ -3933,19 +3725,25 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B65">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>18.728432106945771</v>
+        <v>0.62784849565859768</v>
       </c>
       <c r="D65">
-        <v>0.89183010033075116</v>
+        <v>0.31392424782929879</v>
+      </c>
+      <c r="E65">
+        <v>0.53553828569004103</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0.59313788098617448</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s">
         <v>19</v>
@@ -3953,77 +3751,45 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C66">
-        <v>1.407449454645449</v>
+        <v>12.309874719640179</v>
       </c>
       <c r="D66">
-        <v>1.407449454645449</v>
-      </c>
-      <c r="E66">
-        <v>2.1523604229195241</v>
-      </c>
-      <c r="F66">
-        <v>0.15716815084871341</v>
+        <v>0.58618451045905617</v>
       </c>
       <c r="G66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <v>0.1902120613648251</v>
-      </c>
-      <c r="D67">
-        <v>0.1902120613648251</v>
-      </c>
-      <c r="E67">
-        <v>0.29088427402653882</v>
-      </c>
-      <c r="F67">
-        <v>0.59532715849388307</v>
-      </c>
-      <c r="G67" t="s">
-        <v>18</v>
-      </c>
-      <c r="H67" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>2.8032612628801261</v>
+        <v>56.399980760402791</v>
       </c>
       <c r="D68">
-        <v>1.4016306314400631</v>
+        <v>56.399980760402791</v>
       </c>
       <c r="E68">
-        <v>2.1434619116913578</v>
-      </c>
-      <c r="F68">
-        <v>0.1421983614580456</v>
+        <v>63.240723473547092</v>
+      </c>
+      <c r="F68" s="4">
+        <v>9.0608433113040592E-8</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
         <v>19</v>
@@ -4031,25 +3797,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>2.8415365931114982</v>
+        <v>0.29625220225622462</v>
       </c>
       <c r="D69">
-        <v>2.8415365931114982</v>
+        <v>0.29625220225622462</v>
       </c>
       <c r="E69">
-        <v>4.345456871011721</v>
-      </c>
-      <c r="F69">
-        <v>4.9503523876994207E-2</v>
+        <v>0.33218457433355769</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0.57050203395472754</v>
       </c>
       <c r="G69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
         <v>19</v>
@@ -4057,25 +3823,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>0.45756801409274178</v>
+        <v>3.8403487137522112</v>
       </c>
       <c r="D70">
-        <v>0.22878400704637089</v>
+        <v>1.9201743568761049</v>
       </c>
       <c r="E70">
-        <v>0.34987092469874692</v>
-      </c>
-      <c r="F70">
-        <v>0.70880967686925822</v>
+        <v>2.1530719317098339</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0.14106844592515019</v>
       </c>
       <c r="G70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
         <v>19</v>
@@ -4083,25 +3849,25 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>1.8893688926588259</v>
+        <v>0.44549894357860231</v>
       </c>
       <c r="D71">
-        <v>0.94468444632941306</v>
+        <v>0.44549894357860231</v>
       </c>
       <c r="E71">
-        <v>1.444671002369518</v>
-      </c>
-      <c r="F71">
-        <v>0.25832035053638919</v>
+        <v>0.49953342392612787</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.48747423121554229</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s">
         <v>19</v>
@@ -4109,25 +3875,25 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>0.69679083171592027</v>
+        <v>3.0019840314486288</v>
       </c>
       <c r="D72">
-        <v>0.34839541585796008</v>
+        <v>1.5009920157243151</v>
       </c>
       <c r="E72">
-        <v>0.53278823061405289</v>
-      </c>
-      <c r="F72">
-        <v>0.59469211114133191</v>
+        <v>1.6830470458079909</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0.2099183803408276</v>
       </c>
       <c r="G72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s">
         <v>19</v>
@@ -4135,25 +3901,280 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>2.107882035430896</v>
+      </c>
+      <c r="D73">
+        <v>1.053941017715448</v>
+      </c>
+      <c r="E73">
+        <v>1.1817733190711719</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0.32632136311739951</v>
+      </c>
+      <c r="G73" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74">
+        <v>1.373112593237271</v>
+      </c>
+      <c r="D74">
+        <v>0.68655629661863538</v>
+      </c>
+      <c r="E74">
+        <v>0.76982857650130188</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0.47572490058145211</v>
+      </c>
+      <c r="G74" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>13</v>
       </c>
-      <c r="B73">
+      <c r="B75">
         <v>21</v>
       </c>
-      <c r="C73">
+      <c r="C75">
+        <v>18.728432106945771</v>
+      </c>
+      <c r="D75">
+        <v>0.89183010033075116</v>
+      </c>
+      <c r="G75" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>1.407449454645449</v>
+      </c>
+      <c r="D77">
+        <v>1.407449454645449</v>
+      </c>
+      <c r="E77">
+        <v>2.1523604229195241</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0.15716815084871341</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>0.1902120613648251</v>
+      </c>
+      <c r="D78">
+        <v>0.1902120613648251</v>
+      </c>
+      <c r="E78">
+        <v>0.29088427402653882</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0.59532715849388307</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79">
+        <v>2.8032612628801261</v>
+      </c>
+      <c r="D79">
+        <v>1.4016306314400631</v>
+      </c>
+      <c r="E79">
+        <v>2.1434619116913578</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0.1421983614580456</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>2.8415365931114982</v>
+      </c>
+      <c r="D80">
+        <v>2.8415365931114982</v>
+      </c>
+      <c r="E80">
+        <v>4.345456871011721</v>
+      </c>
+      <c r="F80" s="4">
+        <v>4.9503523876994207E-2</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+      <c r="C81">
+        <v>0.45756801409274178</v>
+      </c>
+      <c r="D81">
+        <v>0.22878400704637089</v>
+      </c>
+      <c r="E81">
+        <v>0.34987092469874692</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0.70880967686925822</v>
+      </c>
+      <c r="G81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82">
+        <v>1.8893688926588259</v>
+      </c>
+      <c r="D82">
+        <v>0.94468444632941306</v>
+      </c>
+      <c r="E82">
+        <v>1.444671002369518</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0.25832035053638919</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83">
+        <v>0.69679083171592027</v>
+      </c>
+      <c r="D83">
+        <v>0.34839541585796008</v>
+      </c>
+      <c r="E83">
+        <v>0.53278823061405289</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0.59469211114133191</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84">
+        <v>21</v>
+      </c>
+      <c r="C84">
         <v>13.7321046386196</v>
       </c>
-      <c r="D73">
+      <c r="D84">
         <v>0.65390974469617125</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G84" t="s">
         <v>18</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H84" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>